--- a/Outputs/Tables/UnitRoot_ADF.xlsx
+++ b/Outputs/Tables/UnitRoot_ADF.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="29" uniqueCount="20">
   <si>
-    <t>Pruebas ADF — Orden de integración de las variables</t>
+    <t>Pruebas ADF — Orden de integración</t>
   </si>
   <si>
     <t>Variable</t>
@@ -72,7 +72,7 @@
     <t>VC con tendencia: 1% = -3.99   5% = -3.43   10% = -3.13</t>
   </si>
   <si>
-    <t>*** p&lt;0.01  ** p&lt;0.05  * p&lt;0.10. H0: la serie tiene raíz unitaria.</t>
+    <t>*** p&lt;0.01  ** p&lt;0.05  * p&lt;0.10. H0: raíz unitaria.</t>
   </si>
 </sst>
 </file>
